--- a/output/pdf_financials_xlsx/ZBNI.xlsx
+++ b/output/pdf_financials_xlsx/ZBNI.xlsx
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.08254499999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.922185</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.42438</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009363</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006421</v>
       </c>
     </row>
     <row r="35">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.08254499999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.922185</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.42438</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009363</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006421</v>
       </c>
     </row>
     <row r="37">
@@ -1488,19 +1488,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.094545</v>
+        <v>0.012</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.009398</v>
+        <v>0.087213</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.551989</v>
+        <v>0.127609</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.045892</v>
+        <v>0.036529</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.025609</v>
+        <v>0.019188</v>
       </c>
     </row>
     <row r="49">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZBNI.xlsx
+++ b/output/pdf_financials_xlsx/ZBNI.xlsx
@@ -7313,7 +7313,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
